--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122415500</v>
+        <v>122411677</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -708,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480886</v>
+        <v>480923</v>
       </c>
       <c r="R2" t="n">
-        <v>6984500</v>
+        <v>6984583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122411677</v>
+        <v>122412030</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -830,19 +839,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480923</v>
+        <v>481112</v>
       </c>
       <c r="R3" t="n">
-        <v>6984583</v>
+        <v>6984490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -964,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R4" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -842,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R3" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122415500</v>
+        <v>122412030</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -964,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480886</v>
+        <v>481112</v>
       </c>
       <c r="R4" t="n">
-        <v>6984500</v>
+        <v>6984490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122411677</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122415500</v>
+        <v>122412030</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480886</v>
+        <v>481112</v>
       </c>
       <c r="R3" t="n">
-        <v>6984500</v>
+        <v>6984490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R4" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -842,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R3" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122415500</v>
+        <v>122412030</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -964,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480886</v>
+        <v>481112</v>
       </c>
       <c r="R4" t="n">
-        <v>6984500</v>
+        <v>6984490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122411677</v>
+        <v>122412030</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -708,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480923</v>
+        <v>481112</v>
       </c>
       <c r="R2" t="n">
-        <v>6984583</v>
+        <v>6984490</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122415500</v>
+        <v>122411677</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -824,11 +810,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -839,10 +820,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480886</v>
+        <v>480923</v>
       </c>
       <c r="R3" t="n">
-        <v>6984500</v>
+        <v>6984583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -946,11 +936,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -964,7 +949,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R4" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1008,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412030</v>
+        <v>122411677</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -703,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481112</v>
+        <v>480923</v>
       </c>
       <c r="R2" t="n">
-        <v>6984490</v>
+        <v>6984583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122411677</v>
+        <v>122415500</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,6 +824,11 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -820,19 +839,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480923</v>
+        <v>480886</v>
       </c>
       <c r="R3" t="n">
-        <v>6984583</v>
+        <v>6984500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122415500</v>
+        <v>122412030</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,6 +946,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -949,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480886</v>
+        <v>481112</v>
       </c>
       <c r="R4" t="n">
-        <v>6984500</v>
+        <v>6984490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122415500</v>
+        <v>122412030</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -842,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480886</v>
+        <v>481112</v>
       </c>
       <c r="R3" t="n">
-        <v>6984500</v>
+        <v>6984490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -964,7 +964,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R4" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122411677</v>
+        <v>122415500</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480923</v>
+        <v>480886</v>
       </c>
       <c r="R2" t="n">
-        <v>6984583</v>
+        <v>6984500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -928,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122415500</v>
+        <v>122411677</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -961,10 +952,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480886</v>
+        <v>480923</v>
       </c>
       <c r="R4" t="n">
-        <v>6984500</v>
+        <v>6984583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122415500</v>
+        <v>122411677</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -708,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480886</v>
+        <v>480923</v>
       </c>
       <c r="R2" t="n">
-        <v>6984500</v>
+        <v>6984583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -833,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R3" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122411677</v>
+        <v>122412030</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -952,19 +961,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480923</v>
+        <v>481112</v>
       </c>
       <c r="R4" t="n">
-        <v>6984583</v>
+        <v>6984490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122411677</v>
+        <v>122415500</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,19 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480923</v>
+        <v>480886</v>
       </c>
       <c r="R2" t="n">
-        <v>6984583</v>
+        <v>6984500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,7 +800,7 @@
         <v>122412030</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -928,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122415500</v>
+        <v>122411677</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,10 +952,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480886</v>
+        <v>480923</v>
       </c>
       <c r="R4" t="n">
-        <v>6984500</v>
+        <v>6984583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122415500</v>
+        <v>122411677</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -708,10 +708,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480886</v>
+        <v>480923</v>
       </c>
       <c r="R2" t="n">
-        <v>6984500</v>
+        <v>6984583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
+          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412030</v>
+        <v>122415500</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -833,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481112</v>
+        <v>480886</v>
       </c>
       <c r="R3" t="n">
-        <v>6984490</v>
+        <v>6984500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på många av granarna här längs Karsån.</t>
+          <t>Bohål cirka två meter upp i stående död gran. Rätt färskt, möjligen uthackat under 2024. Mycket talar för tretå (som födosökte i närheten), men kanske svårt satt säkert utesluta större hack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122411677</v>
+        <v>122412030</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -952,19 +961,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480923</v>
+        <v>481112</v>
       </c>
       <c r="R4" t="n">
-        <v>6984583</v>
+        <v>6984490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosök på stående död gran. Flera granar i skogen uppvisar färska spår av födosökande tretåig hackspett.</t>
+          <t>Ringhack på många av granarna här längs Karsån.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122415500</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122415500</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122415500</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122415500</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,598 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126615896</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91541</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Karsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984589</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126615868</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91699</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984589</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126615937</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Karsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984589</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126616665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96614</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Karsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984589</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126616196</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91259</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Karsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984589</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126616406</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Karsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480997</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984589</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack i gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126616196</v>
+        <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>91259</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,24 +1449,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1509,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126616406</v>
+        <v>126616196</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,29 +1556,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1611,11 +1616,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>126615896</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>126615868</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126615937</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>126616665</v>
       </c>
       <c r="B8" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126616196</v>
+        <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>91259</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,24 +1449,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1509,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126616406</v>
+        <v>126616196</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,29 +1556,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1611,11 +1616,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>126615896</v>
       </c>
       <c r="B5" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>126615868</v>
       </c>
       <c r="B6" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126615937</v>
       </c>
       <c r="B7" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>126616665</v>
       </c>
       <c r="B8" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126616406</v>
+        <v>126616196</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,29 +1449,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1514,11 +1509,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126616196</v>
+        <v>126616406</v>
       </c>
       <c r="B10" t="n">
-        <v>91333</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,24 +1546,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1616,6 +1611,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126616196</v>
+        <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>91339</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,24 +1449,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1509,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126616406</v>
+        <v>126616196</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,29 +1556,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Karsån, Jmt</t>
@@ -1611,11 +1616,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack i gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1441,7 +1441,7 @@
         <v>126616406</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>126615896</v>
       </c>
       <c r="B5" t="n">
-        <v>91621</v>
+        <v>91615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>126615868</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126615937</v>
       </c>
       <c r="B7" t="n">
-        <v>91325</v>
+        <v>91319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>126616665</v>
       </c>
       <c r="B8" t="n">
-        <v>96695</v>
+        <v>96689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>126616196</v>
       </c>
       <c r="B10" t="n">
-        <v>91339</v>
+        <v>91333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 3995-2025 artfynd.xlsx
+++ b/artfynd/A 3995-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>126615896</v>
       </c>
       <c r="B5" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>126615868</v>
       </c>
       <c r="B6" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126615937</v>
       </c>
       <c r="B7" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>126616665</v>
       </c>
       <c r="B8" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>126616196</v>
       </c>
       <c r="B10" t="n">
-        <v>91333</v>
+        <v>91339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
